--- a/datos_con_zscores.xlsx
+++ b/datos_con_zscores.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP37"/>
+  <dimension ref="A1:AP43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1592,22 +1592,22 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>lucas Beatriz Hermelida</t>
+          <t>ACEVEDO BELEN MARTA LUCIA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DNT cronica </t>
+          <t>DNT  AGUDA</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">SNG </t>
+          <t>SNG</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>59711607</t>
+          <t>59620494</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1617,162 +1617,136 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monte Sinai Salvador Mazzas pocitos </t>
+          <t>POZO EL TIGRE SVE</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Consultorios Externos</t>
+          <t>PASE DE SALA DE PEDIATRIA</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2022-12-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>1 A 6 M 14 D</t>
-        </is>
-      </c>
+          <t>2022-10-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>3.070</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>49</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="N8" s="2" t="n">
-        <v>45441</v>
+        <v>45707</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>6600</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>83</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>IMC 12,9 -2,38</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>0.77</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="n">
-        <v>45471</v>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>8.81</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>-1.3</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>-2.32</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>-2.72</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>Sanchez Beatriz</t>
+          <t>ACEVEDO ROSMARY</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DNT cronica agudizada calorica proteica moderada </t>
+          <t xml:space="preserve">DESNUTRICION AGUDA MODERADA TBC E/E GEA TRASTORNO DEL MEDIO INTERNO </t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>DNT CRONICA EN TTO</t>
+          <t xml:space="preserve">INTERNADA </t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Formula Entera v.o 150cc/toma al 15% </t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr"/>
+          <t>FORMULA INDICADA EN INTERNACION F75 F100</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>WHICHI</t>
+        </is>
+      </c>
       <c r="AI8" t="n">
         <v>1</v>
       </c>
-      <c r="AJ8" t="n">
-        <v>30</v>
-      </c>
+      <c r="AJ8" t="inlineStr"/>
       <c r="AK8" t="n">
-        <v>-3.631609846000241</v>
+        <v>-2.75688720808069</v>
       </c>
       <c r="AL8" t="n">
-        <v>-3.119377248464948</v>
+        <v>-1.78282942084902</v>
       </c>
       <c r="AM8" t="n">
-        <v>-2.261859876363644</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>-1.279713208835925</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>-2.724729586789385</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0.5838807575034001</v>
+        <v>-2.382204622203766</v>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secretario Dana Veronica </t>
+          <t>lucas Beatriz Hermelida</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1782,12 +1756,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SNG</t>
+          <t xml:space="preserve">SNG </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>59759459</t>
+          <t>59711607</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1797,229 +1771,221 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Comunidad Pablo Secretario Tartagal</t>
+          <t xml:space="preserve">Monte Sinai Salvador Mazzas pocitos </t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ConsultoriosExternos</t>
+          <t>Consultorios Externos</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2023-01-25 00:00:00</t>
+          <t>2022-12-21 00:00:00</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1 A 6 M 29 D</t>
+          <t>1 A 6 M 14 D</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>3.070</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>46</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="N9" s="2" t="n">
-        <v>45510</v>
+        <v>45441</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>7890</t>
+          <t>6600</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>71</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="U9" s="2" t="n">
-        <v>45527</v>
+        <v>45471</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>9440</t>
+          <t>8.81</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>73</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.04</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>1555</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>Perez Esilda</t>
+          <t>Sanchez Beatriz</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>DNT cronica  Calorica Proteica leve - Diarrea Intrmitente - Pio dermititis - Alto Rieso Social</t>
+          <t xml:space="preserve">DNT cronica agudizada calorica proteica moderada </t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>Bronquioliti aguda no especificada Recuperada Nutricional</t>
+          <t>DNT CRONICA EN TTO</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Formula de leche entera 0%  lactossa + dieta astringente </t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>wichi</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Formula Entera v.o 150cc/toma al 15% </t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="n">
         <v>1</v>
       </c>
       <c r="AJ9" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="AK9" t="n">
-        <v>-2.250213652068871</v>
+        <v>-3.631609846000241</v>
       </c>
       <c r="AL9" t="n">
-        <v>-2.421614408794121</v>
+        <v>-3.119377248464948</v>
       </c>
       <c r="AM9" t="n">
-        <v>-1.013802589395394</v>
+        <v>-2.261859876363644</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.8157015567438211</v>
+        <v>-1.279713208835925</v>
       </c>
       <c r="AO9" t="n">
-        <v>-2.248095066375204</v>
+        <v>-2.724729586789385</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.7896403828531307</v>
+        <v>0.5838807575034001</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Gavi Adolfo Belarde</t>
+          <t xml:space="preserve">Secretario Dana Veronica </t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DNTcronica</t>
+          <t xml:space="preserve">DNT cronica </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>via oral</t>
+          <t>SNG</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>59760007</t>
+          <t>59759459</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alto La sierra Dpto Rivadavia</t>
+          <t>Comunidad Pablo Secretario Tartagal</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pediatria 1° Piso Tartagal</t>
+          <t>ConsultoriosExternos</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2023-07-21 00:00:00</t>
+          <t>2023-01-25 00:00:00</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1 A 1 M 2 D</t>
+          <t>1 A 6 M 29 D</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>49</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>41</t>
         </is>
       </c>
       <c r="N10" s="2" t="n">
-        <v>45511</v>
+        <v>45510</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -2028,90 +1994,90 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="U10" s="2" t="n">
-        <v>45517</v>
+        <v>45527</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>8250</t>
+          <t>9440</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>75</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>1555</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Suarez Beatriz </t>
+          <t>Perez Esilda</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t xml:space="preserve">DNT cronica Calorica Leve - Anemia Cronica -GEA Trastornos del Medio Interno </t>
+          <t>DNT cronica  Calorica Proteica leve - Diarrea Intrmitente - Pio dermititis - Alto Rieso Social</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>DNT Proteica Calorica Leve</t>
+          <t>Bronquioliti aguda no especificada Recuperada Nutricional</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Formula de leche Entera al 15% ´azucar 4% 200cc x 5/T/diarias + dieta hipercalorica monoproteica c/ colaciones </t>
+          <t xml:space="preserve">Formula de leche entera 0%  lactossa + dieta astringente </t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
@@ -2123,47 +2089,47 @@
         <v>1</v>
       </c>
       <c r="AJ10" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="AK10" t="n">
-        <v>-1.951675814613705</v>
+        <v>-2.250213652068871</v>
       </c>
       <c r="AL10" t="n">
-        <v>-1.844074227606965</v>
+        <v>-2.421614408794121</v>
       </c>
       <c r="AM10" t="n">
-        <v>-1.204267899480459</v>
+        <v>-1.013802589395394</v>
       </c>
       <c r="AN10" t="n">
-        <v>-1.589177503824124</v>
+        <v>-0.8157015567438211</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.9668947254546931</v>
+        <v>-2.248095066375204</v>
       </c>
       <c r="AP10" t="n">
-        <v>-3.080302782141584</v>
+        <v>0.7896403828531307</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BASUALDO SAMUEL LUCINDO</t>
+          <t>Gavi Adolfo Belarde</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DNT CRONICA REAGUDIZADA</t>
+          <t>DNTcronica</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SNG</t>
+          <t>via oral</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>59760021</t>
+          <t>59760007</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2173,163 +2139,175 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ALTO LA SIERRA</t>
+          <t>Alto La sierra Dpto Rivadavia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>PASE HOSPITAL ALTO LA SIERRA</t>
+          <t>Pediatria 1° Piso Tartagal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2023-12-15 00:00:00</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+          <t>2023-07-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>1 A 1 M 2 D</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>43</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>36</t>
         </is>
       </c>
       <c r="N11" s="2" t="n">
-        <v>45665</v>
+        <v>45511</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>7890</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="U11" s="2" t="n">
-        <v>45679</v>
+        <v>45517</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8250</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>79</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
+          <t>0.91</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIRANDA BEATRIZ </t>
+          <t xml:space="preserve">Suarez Beatriz </t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> DESNUTRICIÓN CRÓNICA MODERADA REAGUDIZADA, ARS</t>
+          <t xml:space="preserve">DNT cronica Calorica Leve - Anemia Cronica -GEA Trastornos del Medio Interno </t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t xml:space="preserve">RECUPERADO NUTRICIONALMENTE </t>
+          <t>DNT Proteica Calorica Leve</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t xml:space="preserve">FORMULA INDICADA EN INTERNACION F100 </t>
+          <t xml:space="preserve">Formula de leche Entera al 15% ´azucar 4% 200cc x 5/T/diarias + dieta hipercalorica monoproteica c/ colaciones </t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>WHICHI</t>
+          <t>wichi</t>
         </is>
       </c>
       <c r="AI11" t="n">
         <v>1</v>
       </c>
       <c r="AJ11" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="AK11" t="n">
-        <v>-3.062118536295415</v>
+        <v>-1.951675814613705</v>
       </c>
       <c r="AL11" t="n">
-        <v>-2.359622985455327</v>
+        <v>-1.844074227606965</v>
       </c>
       <c r="AM11" t="n">
-        <v>-2.383465254609526</v>
+        <v>-1.204267899480459</v>
       </c>
       <c r="AN11" t="n">
-        <v>-1.68845849860794</v>
+        <v>-1.589177503824124</v>
       </c>
       <c r="AO11" t="n">
-        <v>-2.144206731955196</v>
+        <v>0.9668947254546931</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.5656056861715025</v>
+        <v>-3.080302782141584</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rasputin Mendoza Luciana Sara</t>
+          <t>GABY ADOLFO BELARDO</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">DNT cronica </t>
+          <t>DNT CRONICA REAGUDIZADA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2339,173 +2317,173 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>59812431</t>
+          <t>59760007</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Jerusalem y Mateo Mision Cherenta Tartagal</t>
+          <t xml:space="preserve">ALTO LA SIERRA </t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Pediatria 1° Piso</t>
+          <t>DERIVACION  A.O ALTO LA SIERRA</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2023-02-15 00:00:00</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>1 A 4 M 20 D</t>
-        </is>
-      </c>
+          <t>2023-07-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2,06</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="N12" s="2" t="n">
-        <v>45435</v>
+        <v>45712</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>6640</t>
+          <t>7.97</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>77</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-2.71</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>80</t>
         </is>
       </c>
       <c r="U12" s="2" t="n">
-        <v>45477</v>
+        <v>45727</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>8.69</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>95</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>Rasputin Florencia Carla</t>
+          <t>SUAREZ BEATRIZ</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>GEA con Deshidratacion severa-DNT cronica Reagudizada -IRA-Trastornos del medio Inerno</t>
+          <t xml:space="preserve"> DESNUTRICIÓN CALORICA SEVERA CON BAJA TALLA. GEA. TRASTORNO DEL MEDIO INTERNO HIPOKALEMIA, IRAB,ARS</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>RECUPERADA NUTRICIONALMENTE , CELIAQUIA Y APLV E/E</t>
+          <t xml:space="preserve">RECUPERADO NUTRICIONALMENTE </t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t xml:space="preserve">LECHE 0% LACTOSA EN FORMA DE PREPARACIONES </t>
-        </is>
-      </c>
-      <c r="AH12" t="inlineStr"/>
+          <t>FORMULA INDICADA EN INTERNACION F75 F100</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>WHICHI</t>
+        </is>
+      </c>
       <c r="AI12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ12" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="AK12" t="n">
-        <v>-3.176258538320726</v>
+        <v>-3.023212558463716</v>
       </c>
       <c r="AL12" t="n">
-        <v>-1.72479371765982</v>
+        <v>-2.321734911724203</v>
       </c>
       <c r="AM12" t="n">
-        <v>-3.021042831895146</v>
+        <v>-2.365683321858234</v>
       </c>
       <c r="AN12" t="n">
-        <v>-1.108346775284119</v>
+        <v>-1.412294438600552</v>
       </c>
       <c r="AO12" t="n">
-        <v>-1.499825436905249</v>
+        <v>-1.930069616626953</v>
       </c>
       <c r="AP12" t="n">
-        <v>-0.2942374639917902</v>
+        <v>-0.3014300483288751</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Arce Fernanda sisiana Rosaly</t>
+          <t>BASUALDO SAMUEL LUCINDO</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DNT cronica</t>
+          <t>DNT CRONICA REAGUDIZADA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2515,37 +2493,33 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>59813347</t>
+          <t>59760021</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Paraje TONONO Tartagal</t>
+          <t>ALTO LA SIERRA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Pediatria 1° Piso Tartagal</t>
+          <t>PASE HOSPITAL ALTO LA SIERRA</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2023-03-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>1 A 5 M 13 D</t>
-        </is>
-      </c>
+          <t>2023-12-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2555,117 +2529,147 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="N13" s="2" t="n">
-        <v>45509</v>
+        <v>45665</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>7690</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>71</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>-2.31</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
+          <t>-2.36</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="n">
+        <v>45679</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>8.25</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>-0.57</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>-1.6</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>-2.14</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>Arce Dina Rebeca</t>
+          <t xml:space="preserve">MIRANDA BEATRIZ </t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>DNT croncia Calorica Pediatrica Leve - Anemia Moderada Alto RiesgoSocial</t>
+          <t xml:space="preserve"> DESNUTRICIÓN CRÓNICA MODERADA REAGUDIZADA, ARS</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>Continua Internado</t>
-        </is>
-      </c>
-      <c r="AG13" t="inlineStr"/>
+          <t xml:space="preserve">RECUPERADO NUTRICIONALMENTE </t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FORMULA INDICADA EN INTERNACION F100 </t>
+        </is>
+      </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>wichi</t>
+          <t>WHICHI</t>
         </is>
       </c>
       <c r="AI13" t="n">
         <v>1</v>
       </c>
-      <c r="AJ13" t="inlineStr"/>
+      <c r="AJ13" t="n">
+        <v>14</v>
+      </c>
       <c r="AK13" t="n">
-        <v>-2.206857181666729</v>
+        <v>-3.062118536295415</v>
       </c>
       <c r="AL13" t="n">
-        <v>-2.304487307068142</v>
+        <v>-2.359622985455327</v>
       </c>
       <c r="AM13" t="n">
-        <v>-1.083356611468988</v>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
+        <v>-2.383465254609526</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-1.68845849860794</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>-2.144206731955196</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>-0.5656056861715025</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MAMANI YESENIA ZAMIRA VIVIANA</t>
+          <t>Rasputin Mendoza Luciana Sara</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">DNT CRONICA </t>
+          <t xml:space="preserve">DNT cronica </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">V. O </t>
+          <t>SNG</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>59866527</t>
+          <t>59812431</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2675,163 +2679,163 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>MOSCONI</t>
+          <t>Jerusalem y Mateo Mision Cherenta Tartagal</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>PASE DE SALA DE PEDOATRIA</t>
+          <t>Pediatria 1° Piso</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2024-11-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
+          <t>2023-02-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>1 A 4 M 20 D</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>3.41</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>2,06</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>35</t>
         </is>
       </c>
       <c r="N14" s="2" t="n">
-        <v>45659</v>
+        <v>45435</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>8.83</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="U14" s="2" t="n">
-        <v>45667</v>
+        <v>45477</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>9.67</t>
+          <t>8.69</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>75</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>MAMANI GABRIELA</t>
+          <t>Rasputin Florencia Carla</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>DESNUTRICIÓN CRÓNICA LEVE, ANEMIA CRONICA, DIARREA CRONICA</t>
+          <t>GEA con Deshidratacion severa-DNT cronica Reagudizada -IRA-Trastornos del medio Inerno</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>RECUPERADA NUTRICIONALMENTE INTOLERANCIA A LA LACTOSA TRANSITORIA</t>
+          <t>RECUPERADA NUTRICIONALMENTE , CELIAQUIA Y APLV E/E</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t xml:space="preserve">FORMUAL ENTERA 0% LACTOSA 200C/TOMA AL 15% V.O </t>
-        </is>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WHICHI </t>
-        </is>
-      </c>
+          <t xml:space="preserve">LECHE 0% LACTOSA EN FORMA DE PREPARACIONES </t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="n">
         <v>1</v>
       </c>
       <c r="AJ14" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="AK14" t="n">
-        <v>5.23954504041986</v>
+        <v>-3.176258538320726</v>
       </c>
       <c r="AL14" t="n">
-        <v>10.68016505936436</v>
+        <v>-1.72479371765982</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.1639606437514298</v>
+        <v>-3.021042831895146</v>
       </c>
       <c r="AN14" t="n">
-        <v>5.583979280004538</v>
+        <v>-1.108346775284119</v>
       </c>
       <c r="AO14" t="n">
-        <v>11.11404703335455</v>
+        <v>-1.499825436905249</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.3561612982742025</v>
+        <v>-0.2942374639917902</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Diaz Yeimi Irene </t>
+          <t>Arce Fernanda sisiana Rosaly</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>DNT CRONICA</t>
+          <t>DNT cronica</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2841,7 +2845,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>59938632</t>
+          <t>59813347</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2851,68 +2855,68 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>M EL CRUCE MOSCONI</t>
+          <t>Paraje TONONO Tartagal</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Consultorios Externos</t>
+          <t>Pediatria 1° Piso Tartagal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2022-06-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
+          <t>2023-03-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1 A 5 M 13 D</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>3,09</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>48</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>40</t>
         </is>
       </c>
       <c r="N15" s="2" t="n">
-        <v>45481</v>
+        <v>45509</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>7690</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>73</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>-2.81</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>0.88</t>
-        </is>
-      </c>
+          <t>-2.31</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
@@ -2924,37 +2928,37 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>Romero Adriana</t>
+          <t>Arce Dina Rebeca</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>Desnutricon Cronica Calorica secundaria - Trastorno deglutorio - ecne - RMG -SBOR</t>
+          <t>DNT croncia Calorica Pediatrica Leve - Anemia Moderada Alto RiesgoSocial</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t xml:space="preserve">continua internada </t>
-        </is>
-      </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>formula de inicio</t>
-        </is>
-      </c>
-      <c r="AH15" t="inlineStr"/>
+          <t>Continua Internado</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>wichi</t>
+        </is>
+      </c>
       <c r="AI15" t="n">
         <v>1</v>
       </c>
       <c r="AJ15" t="inlineStr"/>
       <c r="AK15" t="n">
-        <v>-5.044256830597924</v>
+        <v>-2.206857181666729</v>
       </c>
       <c r="AL15" t="n">
-        <v>-5.699066803934732</v>
+        <v>-2.304487307068142</v>
       </c>
       <c r="AM15" t="n">
-        <v>-1.121759708759227</v>
+        <v>-1.083356611468988</v>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
@@ -2976,57 +2980,53 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lopez Herrera Roman Armando</t>
+          <t>MAMANI YESENIA ZAMIRA VIVIANA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>DNT cronica</t>
+          <t xml:space="preserve">DNT CRONICA </t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>via oral</t>
+          <t xml:space="preserve">V. O </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>59938743</t>
+          <t>59866527</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Mision Km 6 Tartagal</t>
+          <t>MOSCONI</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Consultorios Externos</t>
+          <t>PASE DE SALA DE PEDOATRIA</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2023-06-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>1 A 1 M 24 D</t>
-        </is>
-      </c>
+          <t>2024-11-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>3250</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>50</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -3035,145 +3035,133 @@
         </is>
       </c>
       <c r="N16" s="2" t="n">
-        <v>45503</v>
+        <v>45659</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>7400</t>
+          <t>8.83</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>76</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>91</t>
         </is>
       </c>
       <c r="U16" s="2" t="n">
-        <v>45526</v>
+        <v>45667</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>8980</t>
+          <t>9.67</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>78</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1.05</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>1580</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herrera Sandra </t>
+          <t>MAMANI GABRIELA</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>DNT cronica calorica leve - IRAB-Anemia cronica- Enteroparasitosis con antecedentes  de PNT/AEG</t>
+          <t>DESNUTRICIÓN CRÓNICA LEVE, ANEMIA CRONICA, DIARREA CRONICA</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>Bronquitis Aguda debidoa un virus Sincitial Respiratorio</t>
+          <t>RECUPERADA NUTRICIONALMENTE INTOLERANCIA A LA LACTOSA TRANSITORIA</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Formula Leche entera 15% + azucar4% 200cc x 5 tomas /diarias + dieta hipercalorica noroproeica con colaciones </t>
+          <t xml:space="preserve">FORMUAL ENTERA 0% LACTOSA 200C/TOMA AL 15% V.O </t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>wichi</t>
+          <t xml:space="preserve">WHICHI </t>
         </is>
       </c>
       <c r="AI16" t="n">
         <v>1</v>
       </c>
       <c r="AJ16" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="AK16" t="n">
-        <v>-2.615898275432505</v>
+        <v>5.23954504041986</v>
       </c>
       <c r="AL16" t="n">
-        <v>-2.856265813361405</v>
+        <v>10.68016505936436</v>
       </c>
       <c r="AM16" t="n">
-        <v>-1.267164622610851</v>
+        <v>0.1639606437514298</v>
       </c>
       <c r="AN16" t="n">
-        <v>-1.018049059363717</v>
+        <v>5.583979280004538</v>
       </c>
       <c r="AO16" t="n">
-        <v>-2.550919378860142</v>
+        <v>11.11404703335455</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.714016009095631</v>
+        <v>0.3561612982742025</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NICASIO Victoria Arminda</t>
+          <t xml:space="preserve">Diaz Yeimi Irene </t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">DNT cronica  </t>
+          <t>DNT CRONICA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3183,7 +3171,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>59989750</t>
+          <t>59938632</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3193,7 +3181,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Mision Km 7 tartagal</t>
+          <t>M EL CRUCE MOSCONI</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -3203,60 +3191,56 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2023-06-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>1 A 2 M 6 D</t>
-        </is>
-      </c>
+          <t>2022-06-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3,09</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="N17" s="2" t="n">
-        <v>45523</v>
+        <v>45481</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>68</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -3270,37 +3254,37 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pastor Benigna </t>
+          <t>Romero Adriana</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t xml:space="preserve">DNT cronica Caorica Proteica </t>
+          <t>Desnutricon Cronica Calorica secundaria - Trastorno deglutorio - ecne - RMG -SBOR</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>Continua Internado</t>
-        </is>
-      </c>
-      <c r="AG17" t="inlineStr"/>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>wichi</t>
-        </is>
-      </c>
+          <t xml:space="preserve">continua internada </t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>formula de inicio</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="n">
         <v>1</v>
       </c>
       <c r="AJ17" t="inlineStr"/>
       <c r="AK17" t="n">
-        <v>-2.462566050930028</v>
+        <v>-5.044256830597924</v>
       </c>
       <c r="AL17" t="n">
-        <v>-2.784919194017368</v>
+        <v>-5.699066803934732</v>
       </c>
       <c r="AM17" t="n">
-        <v>-1.026448809690991</v>
+        <v>-1.121759708759227</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
@@ -3322,12 +3306,12 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Burgos Marilina Roberta Paola</t>
+          <t xml:space="preserve">VILLA PEREZ AYLIN DEVORA AYELEN </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">DNT aguda </t>
+          <t>RBP</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3337,7 +3321,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>59990369</t>
+          <t>59938636</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3347,351 +3331,325 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Mision Lapacho II Tartagal</t>
+          <t>LAPACHO II</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Consultorios Externos</t>
+          <t>CONSULTORIO EXTERNO</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2023-07-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>1 A 1 M 2 D</t>
-        </is>
-      </c>
+          <t>2023-06-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="N18" s="2" t="n">
-        <v>45488</v>
+        <v>45723</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>7580</t>
+          <t>9.45</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>-0.7</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="n">
-        <v>45509</v>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>8660</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>73.5</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>-0.47</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>-0.44</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>0.26</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>0.99</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
+          <t>-1.65</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>Ceballo Claudia</t>
+          <t xml:space="preserve">PEREZ LORENA </t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>DNT Aguda Calorica Moderada -GEA- Alto Riesgo social</t>
+          <t xml:space="preserve"> DIARREA CRONICA, TRASTORNOS DEL MEDIO INTERNO, RIESGO NUTRICIONAL, DERMATITIS SEBORREICA, ENTEROPARASITOSIS </t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>Dsnutricion Calorica proteica Leve</t>
-        </is>
-      </c>
-      <c r="AG18" t="inlineStr">
-        <is>
-          <t>Formula de leche entera 0% lactosa via enteral + leche materna</t>
-        </is>
-      </c>
+          <t xml:space="preserve">INTERNADA </t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>wichi</t>
+          <t>WHICHI</t>
         </is>
       </c>
       <c r="AI18" t="n">
         <v>1</v>
       </c>
-      <c r="AJ18" t="n">
-        <v>21</v>
-      </c>
+      <c r="AJ18" t="inlineStr"/>
       <c r="AK18" t="n">
-        <v>-1.338949706044041</v>
+        <v>-1.133173124370152</v>
       </c>
       <c r="AL18" t="n">
-        <v>-0.7029686024955781</v>
+        <v>-1.664058064389073</v>
       </c>
       <c r="AM18" t="n">
-        <v>-1.316076908961388</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>-0.372838987441753</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>-0.4387137521807716</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>-0.1842191987350174</v>
+        <v>-0.1485002405117253</v>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">BURGOS MARILINA </t>
+          <t>Lopez Herrera Roman Armando</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DNT AGUDA</t>
+          <t>DNT cronica</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SNG</t>
+          <t>via oral</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>59990369</t>
+          <t>59938743</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>LAPACHO II</t>
+          <t>Mision Km 6 Tartagal</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>CONSULTORIO EXTERNO</t>
+          <t>Consultorios Externos</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2023-07-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
+          <t>2023-06-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>1 A 1 M 24 D</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3250</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>48</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="N19" s="2" t="n">
-        <v>45652</v>
+        <v>45503</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>7.45</t>
+          <t>7400</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>70</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="U19" s="2" t="n">
-        <v>45660</v>
+        <v>45526</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>8980</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr"/>
-      <c r="AC19" t="inlineStr"/>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>1580</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t xml:space="preserve">BURGOS CLAUDIA </t>
+          <t xml:space="preserve">Herrera Sandra </t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>DESNUTRICION AGUDA CALORICA MODERADA, GEA. ALT MB CON HIPOPOTASEMIA SEVERA,IRA, ANEMIA CRONICA,ARS</t>
+          <t>DNT cronica calorica leve - IRAB-Anemia cronica- Enteroparasitosis con antecedentes  de PNT/AEG</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>RECUPERADA NUTRICIONALMENTE</t>
+          <t>Bronquitis Aguda debidoa un virus Sincitial Respiratorio</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>FORMULA ENTERA 200 CC/TOMA AL 15% VIA ORAL</t>
+          <t xml:space="preserve">Formula Leche entera 15% + azucar4% 200cc x 5 tomas /diarias + dieta hipercalorica noroproeica con colaciones </t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>WHICHI</t>
+          <t>wichi</t>
         </is>
       </c>
       <c r="AI19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="AK19" t="n">
-        <v>-2.544529463714754</v>
+        <v>-2.615898275432505</v>
       </c>
       <c r="AL19" t="n">
-        <v>-1.012509842738411</v>
+        <v>-2.856265813361405</v>
       </c>
       <c r="AM19" t="n">
-        <v>-2.788855114250962</v>
+        <v>-1.267164622610851</v>
       </c>
       <c r="AN19" t="n">
-        <v>-0.7142932698467228</v>
+        <v>-1.018049059363717</v>
       </c>
       <c r="AO19" t="n">
-        <v>-1.1025414982227</v>
+        <v>-2.550919378860142</v>
       </c>
       <c r="AP19" t="n">
-        <v>-0.08601204565450141</v>
+        <v>0.714016009095631</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DIAZ ESTRELLA</t>
+          <t>NICASIO Victoria Arminda</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DNT  CRONICA REAG</t>
+          <t xml:space="preserve">DNT cronica  </t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3701,7 +3659,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>59990421</t>
+          <t>59989750</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -3711,163 +3669,141 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>KM6</t>
+          <t>Mision Km 7 tartagal</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>DERIVACION APS</t>
+          <t>Consultorios Externos</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2023-08-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
+          <t>2023-06-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1 A 2 M 6 D</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>47</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="N20" s="2" t="n">
-        <v>45667</v>
+        <v>45523</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>69</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="n">
-        <v>45677</v>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>8.37</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>-0.36</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>-1.58</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>-2.15</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
+          <t>0.87</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>SORUCO TAMARA</t>
+          <t xml:space="preserve">Pastor Benigna </t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>DESNUTRICIÓN CRÓNICA REAGUDIZADA, IRA, DIARREA , ARS</t>
+          <t xml:space="preserve">DNT cronica Caorica Proteica </t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t xml:space="preserve">RECUPERADA NUTRICIONALMENTE </t>
-        </is>
-      </c>
-      <c r="AG20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FORMULA INDICADA EN INTERNACION F100 </t>
-        </is>
-      </c>
+          <t>Continua Internado</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>WHICHI</t>
+          <t>wichi</t>
         </is>
       </c>
       <c r="AI20" t="n">
         <v>1</v>
       </c>
-      <c r="AJ20" t="n">
-        <v>10</v>
-      </c>
+      <c r="AJ20" t="inlineStr"/>
       <c r="AK20" t="n">
-        <v>-3.199220737437265</v>
+        <v>-2.462566050930028</v>
       </c>
       <c r="AL20" t="n">
-        <v>-2.914963432448408</v>
+        <v>-2.784919194017368</v>
       </c>
       <c r="AM20" t="n">
-        <v>-1.868053693327737</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>-1.583670483669166</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>-2.1457587109484</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>-0.3625789867385884</v>
+        <v>-1.026448809690991</v>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tarraga Agustiba Mrtina </t>
+          <t>Burgos Marilina Roberta Paola</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>DNT CRONICA</t>
+          <t xml:space="preserve">DNT aguda </t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3877,17 +3813,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>70039361</t>
+          <t>59990369</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">F </t>
+          <t>F</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>B 9 DE JULIO</t>
+          <t>Mision Lapacho II Tartagal</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3897,127 +3833,165 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2023-08-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
+          <t>2023-07-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>1 A 1 M 2 D</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>3,04</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
       <c r="N21" s="2" t="n">
-        <v>45475</v>
+        <v>45488</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>5.84</t>
+          <t>7580</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>72</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>-3.15</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.79</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="inlineStr"/>
-      <c r="AB21" t="inlineStr"/>
-      <c r="AC21" t="inlineStr"/>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="n">
+        <v>45509</v>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>8660</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>73.5</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>-0.47</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>-0.44</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>0.26</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tarraga Eliana </t>
+          <t>Ceballo Claudia</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>DNT cronica calorica proteica moderada- anemia cronica- bronqueolitis leve - ars</t>
+          <t>DNT Aguda Calorica Moderada -GEA- Alto Riesgo social</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t xml:space="preserve">continua internada </t>
+          <t>Dsnutricion Calorica proteica Leve</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t xml:space="preserve">formula 0% lactosa 120cc/toma al 15% por sng </t>
-        </is>
-      </c>
-      <c r="AH21" t="inlineStr"/>
+          <t>Formula de leche entera 0% lactosa via enteral + leche materna</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>wichi</t>
+        </is>
+      </c>
       <c r="AI21" t="n">
         <v>1</v>
       </c>
-      <c r="AJ21" t="inlineStr"/>
+      <c r="AJ21" t="n">
+        <v>21</v>
+      </c>
       <c r="AK21" t="n">
-        <v>-3.164073407480427</v>
+        <v>-1.338949706044041</v>
       </c>
       <c r="AL21" t="n">
-        <v>-2.651816629536014</v>
+        <v>-0.7029686024955781</v>
       </c>
       <c r="AM21" t="n">
-        <v>-2.13467789127351</v>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="AP21" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
+        <v>-1.316076908961388</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>-0.372838987441753</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>-0.4387137521807716</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>-0.1842191987350174</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GEREZ EDA</t>
+          <t xml:space="preserve">BURGOS MARILINA </t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>DNT CRONICA REAGUDIZADA</t>
+          <t>DNT AGUDA</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4027,7 +4001,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>70096073</t>
+          <t>59990369</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4037,95 +4011,121 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>KM6</t>
+          <t>LAPACHO II</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>DERIVACION APS</t>
+          <t>CONSULTORIO EXTERNO</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2023-11-16 00:00:00</t>
+          <t>2023-07-21 00:00:00</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>50</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
       <c r="N22" s="2" t="n">
-        <v>45664</v>
+        <v>45652</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>7.45</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>77</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="inlineStr"/>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="n">
+        <v>45660</v>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>9.28</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>-0.09</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>-0.7</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>-1.1</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>SORUCO ELIANA</t>
+          <t xml:space="preserve">BURGOS CLAUDIA </t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> DESNUTRICION CRONICA REAGUDIZADA MODERADA A SEVERA, IRA, ARS, DIARREA, HERNIA UMBILICAL REDUCTIBLE</t>
+          <t>DESNUTRICION AGUDA CALORICA MODERADA, GEA. ALT MB CON HIPOPOTASEMIA SEVERA,IRA, ANEMIA CRONICA,ARS</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>INTERNADA</t>
+          <t>RECUPERADA NUTRICIONALMENTE</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t xml:space="preserve">FORMULA INDICADA EN INTERNACION F100 </t>
+          <t>FORMULA ENTERA 200 CC/TOMA AL 15% VIA ORAL</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
@@ -4134,44 +4134,40 @@
         </is>
       </c>
       <c r="AI22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ22" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>8</v>
+      </c>
       <c r="AK22" t="n">
-        <v>-4.159684083406266</v>
+        <v>-2.544529463714754</v>
       </c>
       <c r="AL22" t="n">
-        <v>-2.650201186142484</v>
+        <v>-1.012509842738411</v>
       </c>
       <c r="AM22" t="n">
-        <v>-3.523351113905613</v>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="AP22" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
+        <v>-2.788855114250962</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>-0.7142932698467228</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>-1.1025414982227</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>-0.08601204565450141</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEREZ TORRES MARIA LUCIA </t>
+          <t>DIAZ ESTRELLA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>DNT CRONICA REAG</t>
+          <t>DNT  CRONICA REAG</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4181,7 +4177,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>70096596</t>
+          <t>59990421</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4191,145 +4187,163 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">LA MORA </t>
+          <t>KM6</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>PASE DE SALA DE PEDIATRIA</t>
+          <t>DERIVACION APS</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2023-11-05 00:00:00</t>
+          <t>2023-08-07 00:00:00</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>50</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>40</t>
         </is>
       </c>
       <c r="N23" s="2" t="n">
-        <v>45679</v>
+        <v>45667</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="inlineStr"/>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="n">
+        <v>45677</v>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>8.37</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>-0.36</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>-1.58</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>-2.15</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t xml:space="preserve">TORES LUCIA </t>
+          <t>SORUCO TAMARA</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>DESNUTRICION CRONICA CALORICA MODERADA, GEA, ANEMIA CRONICA</t>
+          <t>DESNUTRICIÓN CRÓNICA REAGUDIZADA, IRA, DIARREA , ARS</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t xml:space="preserve">INTERNDA </t>
+          <t xml:space="preserve">RECUPERADA NUTRICIONALMENTE </t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>FORMLA INDICADA EN INTERNACION F75 F100</t>
+          <t xml:space="preserve">FORMULA INDICADA EN INTERNACION F100 </t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t xml:space="preserve">WHICHI </t>
+          <t>WHICHI</t>
         </is>
       </c>
       <c r="AI23" t="n">
         <v>1</v>
       </c>
-      <c r="AJ23" t="inlineStr"/>
+      <c r="AJ23" t="n">
+        <v>10</v>
+      </c>
       <c r="AK23" t="n">
-        <v>-3.377483421464469</v>
+        <v>-3.199220737437265</v>
       </c>
       <c r="AL23" t="n">
-        <v>-2.59444584578777</v>
+        <v>-2.914963432448408</v>
       </c>
       <c r="AM23" t="n">
-        <v>-2.46713286179858</v>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="AP23" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
+        <v>-1.868053693327737</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>-1.583670483669166</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>-2.1457587109484</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>-0.3625789867385884</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Gerez eda Lucia</t>
+          <t xml:space="preserve">Tarraga Agustiba Mrtina </t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">DNT aguda </t>
+          <t>DNT CRONICA</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4339,17 +4353,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>70096673</t>
+          <t>70039361</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>F</t>
+          <t xml:space="preserve">F </t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Mision km 6 tartagal</t>
+          <t>B 9 DE JULIO</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -4359,22 +4373,18 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2023-11-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>0 A 9 M 7 D</t>
-        </is>
-      </c>
+          <t>2023-08-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3,04</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -4383,36 +4393,36 @@
         </is>
       </c>
       <c r="N24" s="2" t="n">
-        <v>45513</v>
+        <v>45475</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>6500</t>
+          <t>5.84</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>65</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-3.15</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
@@ -4426,37 +4436,37 @@
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Soruco Eliana </t>
+          <t xml:space="preserve">Tarraga Eliana </t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>DNT aguda calorica - Anemia- cronica -IRAB-Alto Riesgo Social</t>
+          <t>DNT cronica calorica proteica moderada- anemia cronica- bronqueolitis leve - ars</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>Continua Internada</t>
-        </is>
-      </c>
-      <c r="AG24" t="inlineStr"/>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>wichi</t>
-        </is>
-      </c>
+          <t xml:space="preserve">continua internada </t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">formula 0% lactosa 120cc/toma al 15% por sng </t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr"/>
       <c r="AI24" t="n">
         <v>1</v>
       </c>
       <c r="AJ24" t="inlineStr"/>
       <c r="AK24" t="n">
-        <v>-1.90116220296562</v>
+        <v>-3.164073407480427</v>
       </c>
       <c r="AL24" t="n">
-        <v>-1.177522742643934</v>
+        <v>-2.651816629536014</v>
       </c>
       <c r="AM24" t="n">
-        <v>-1.678066613548741</v>
+        <v>-2.13467789127351</v>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
@@ -4478,53 +4488,53 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRIAS PATRICIA </t>
+          <t xml:space="preserve">FERNANDEZ JOSE NAHUEL </t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DNT CRONCA REAG</t>
+          <t>DNT CRONICA REAGUDIZADA</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SNG</t>
+          <t>V.O</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>70164487</t>
+          <t>70039478</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>PACARA</t>
+          <t xml:space="preserve">ALTO LA SIERRA </t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>PASE DE SALA DE PDIATRIA</t>
+          <t>DERIVACION A. O ALTO LA SIERRA</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2023-12-19 00:00:00</t>
+          <t>2023-09-14 00:00:00</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -4533,65 +4543,91 @@
         </is>
       </c>
       <c r="N25" s="2" t="n">
-        <v>45674</v>
+        <v>45712</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>7 ( PESO SECO)</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="inlineStr"/>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="n">
+        <v>45728</v>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>9.9</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>78.5</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>-0.33</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>-0.87</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>-1.34</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>TORRES SILVIA</t>
+          <t>FIDELA CIRIACO</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>DESNUTRICIÓN MARASMO KWASHIORKOR, ANEMIA CRÓNICA, GEA Y TRASTORNOS DEL MEDIO INTERNO EN RESOLUCIÓN</t>
+          <t>DESNUTRICION ARMONICA CALORICA LEVE CON RIEGO DE BAJA TALLA,EPILEPSIA E/E, ANEMIA CRONICA MODERADA, DIARREA CRONICA INETRMITENTE, PARASITOSIS INTESTINAL, IRAB ARS</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>INTERNADA</t>
+          <t xml:space="preserve">RECUPERADO NUTRICIONALMENTE </t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>FORMULA INDICCADA EN INTERNACION F100</t>
+          <t xml:space="preserve">FORMULA ENTERA 225 CC/TOMA AL 15% </t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
@@ -4602,46 +4638,38 @@
       <c r="AI25" t="n">
         <v>1</v>
       </c>
-      <c r="AJ25" t="inlineStr"/>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
+      <c r="AJ25" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>-2.16106763234024</v>
       </c>
       <c r="AL25" t="n">
-        <v>-2.355780856305562</v>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="AP25" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
+        <v>-1.929126923988757</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>-1.423097976727642</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>-0.880564171588556</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>-1.361367232717843</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>-0.06485724609531948</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isquica Martina </t>
+          <t>GEREZ EDA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dnt cronica </t>
+          <t>DNT CRONICA REAGUDIZADA</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4651,7 +4679,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>70197551</t>
+          <t>70096073</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -4661,66 +4689,66 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>B LA MERCED MOSCONI</t>
+          <t>KM6</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Consultorios Externos</t>
+          <t>DERIVACION APS</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2024-01-19 00:00:00</t>
+          <t>2023-11-16 00:00:00</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>3,100</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>51</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
       <c r="N26" s="2" t="n">
-        <v>45468</v>
+        <v>45664</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>69</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>71</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
@@ -4734,37 +4762,41 @@
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Villareal Silvia </t>
+          <t>SORUCO ELIANA</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t xml:space="preserve">DNT Aguda Calorica Moderada - Retraso del Neurodesarrollo -Microcefalia-Quiste simple Hepatico- Trastorno Deglutorio en estudio </t>
+          <t xml:space="preserve"> DESNUTRICION CRONICA REAGUDIZADA MODERADA A SEVERA, IRA, ARS, DIARREA, HERNIA UMBILICAL REDUCTIBLE</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>Continua Internada</t>
+          <t>INTERNADA</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t xml:space="preserve">formula de inicio </t>
-        </is>
-      </c>
-      <c r="AH26" t="inlineStr"/>
+          <t xml:space="preserve">FORMULA INDICADA EN INTERNACION F100 </t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>WHICHI</t>
+        </is>
+      </c>
       <c r="AI26" t="n">
         <v>1</v>
       </c>
       <c r="AJ26" t="inlineStr"/>
       <c r="AK26" t="n">
-        <v>-3.455554733310162</v>
+        <v>-4.159684083406266</v>
       </c>
       <c r="AL26" t="n">
-        <v>-1.513504153567803</v>
+        <v>-2.650201186142484</v>
       </c>
       <c r="AM26" t="n">
-        <v>-3.492394262259693</v>
+        <v>-3.523351113905613</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
@@ -4786,12 +4818,12 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gonzalez Luis Antonio </t>
+          <t xml:space="preserve">PEREZ TORRES MARIA LUCIA </t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>DNT cronica</t>
+          <t>DNT CRONICA REAG</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4801,76 +4833,76 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>70198574</t>
+          <t>70096596</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>MISION LA PAZ SVE</t>
+          <t xml:space="preserve">LA MORA </t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTI PEDIATRIA </t>
+          <t>PASE DE SALA DE PEDIATRIA</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2024-04-27 00:00:00</t>
+          <t>2023-11-05 00:00:00</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2,85</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>49</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
       <c r="N27" s="2" t="n">
-        <v>45462</v>
+        <v>45679</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>70</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>-4.2</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>78</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
@@ -4884,37 +4916,41 @@
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gonzalez Nilda </t>
+          <t xml:space="preserve">TORES LUCIA </t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t xml:space="preserve">DNT cronica calorica proteica severasecundaria- Cardiopatia congenita- sindrome genetico e/e </t>
+          <t>DESNUTRICION CRONICA CALORICA MODERADA, GEA, ANEMIA CRONICA</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>Continua Internado</t>
+          <t xml:space="preserve">INTERNDA </t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t xml:space="preserve">formula de inicio 60cc/toma al 18% cada 3hs </t>
-        </is>
-      </c>
-      <c r="AH27" t="inlineStr"/>
+          <t>FORMLA INDICADA EN INTERNACION F75 F100</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WHICHI </t>
+        </is>
+      </c>
       <c r="AI27" t="n">
         <v>1</v>
       </c>
       <c r="AJ27" t="inlineStr"/>
       <c r="AK27" t="n">
-        <v>-5.279718403685267</v>
+        <v>-3.377483421464469</v>
       </c>
       <c r="AL27" t="n">
-        <v>-4.301158816410321</v>
+        <v>-2.59444584578777</v>
       </c>
       <c r="AM27" t="n">
-        <v>-4.385695332172435</v>
+        <v>-2.46713286179858</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
@@ -4935,162 +4971,144 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GONZALEZ  Luis Antonio</t>
+          <t>Gerez eda Lucia</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>DNT cronica</t>
+          <t xml:space="preserve">DNT aguda </t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>SGN</t>
+          <t>SNG</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>70198574</t>
+          <t>70096673</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Mision La Paz Santa Victoria Este</t>
+          <t>Mision km 6 tartagal</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>HPMI Salta</t>
+          <t>Consultorios Externos</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2024-04-27 00:00:00</t>
+          <t>2023-11-16 00:00:00</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0 A 3 M 27 D</t>
+          <t>0 A 9 M 7 D</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2.285</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>51</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>39</t>
         </is>
       </c>
       <c r="N28" s="2" t="n">
-        <v>45526</v>
-      </c>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
+        <v>45513</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>6500</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>-1.68</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>-1.17</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
       <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Formula de inicioal 18% 70cc cada 3 hs x 8 tomas mas lactancia materna</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>Formula de inicioal 18% 70cc cada 3 hs x 8 tomas mas lactancia materna</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>Formula de inicioal 18% 70cc cada 3 hs x 8 tomas mas lactancia materna</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>Formula de inicioal 18% 70cc cada 3 hs x 8 tomas mas lactancia materna</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>Formula de inicioal 18% 70cc cada 3 hs x 8 tomas mas lactancia materna</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>Formula de inicioal 18% 70cc cada 3 hs x 8 tomas mas lactancia materna</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>Formula de inicioal 18% 70cc cada 3 hs x 8 tomas mas lactancia materna</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Formula de inicioal 18% 70cc cada 3 hs x 8 tomas mas lactancia materna</t>
-        </is>
-      </c>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>Formula de inicioal 18% 70cc cada 3 hs x 8 tomas mas lactancia materna</t>
+          <t xml:space="preserve">Soruco Eliana </t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>Formula de inicioal 18% 70cc cada 3 hs x 8 tomas mas lactancia materna</t>
+          <t>DNT aguda calorica - Anemia- cronica -IRAB-Alto Riesgo Social</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>Formula de inicioal 18% 70cc cada 3 hs x 8 tomas mas lactancia materna</t>
-        </is>
-      </c>
-      <c r="AG28" t="inlineStr">
-        <is>
-          <t>Formula de inicioal 18% 70cc cada 3 hs x 8 tomas mas lactancia materna</t>
-        </is>
-      </c>
+          <t>Continua Internada</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr"/>
       <c r="AH28" t="inlineStr">
         <is>
           <t>wichi</t>
         </is>
       </c>
       <c r="AI28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ28" t="inlineStr"/>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="AL28" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
+      <c r="AK28" t="n">
+        <v>-1.90116220296562</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>-1.177522742643934</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>-1.678066613548741</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
@@ -5112,12 +5130,12 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ORQUIZO NICOLE</t>
+          <t xml:space="preserve">GARCIA KEYTAN LELVIN EUTICO </t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>DNT CRONICA</t>
+          <t>DNT AGUDA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5127,174 +5145,169 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>70198781</t>
+          <t>70096717</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>S.V.E</t>
+          <t>POZO EL TIGRE SVE</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>PASE DE SALA PEDIATRIA</t>
+          <t>PASE DE SALA DE PEDIATRIA</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2024-02-10 00:00:00</t>
+          <t>2023-12-05 00:00:00</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" s="2" t="n">
-        <v>45644</v>
+        <v>45707</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>7.83</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>78</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>P 10</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>74</t>
         </is>
       </c>
       <c r="U29" s="2" t="n">
-        <v>45670</v>
+        <v>45730</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>5.51</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>P 25  50</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>P 10   25</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>P25</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORQUIZO MARCELA </t>
+          <t>GARCIA PASCUALA</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>ECNE, DISPLASIA BRONCOPULMONAR, GASTROTOMIA, RGE SEVERO, DESNUTRICIÓN CRÓNICA MODERADA
-2RIA,TRASTORNOS DEGLUTORIOS, ARS</t>
+          <t>DESNUTRICION AGUDA SEVERA TRASTORNO DEL MEDIO INTERNO SEVERO</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t xml:space="preserve">DESNUTRICION CRONICA EN RECUPERACION </t>
+          <t xml:space="preserve">RECUPERADO NUTRICIONALMENTE </t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t xml:space="preserve">FORMULA DE INICIO 140CC/TOMA AL 22% 6 TOMAS /D SNG </t>
+          <t>FORMULA INDICADA EN INTERNACION F75 F100</t>
         </is>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>CHOROTE</t>
+          <t xml:space="preserve">WHICHI </t>
         </is>
       </c>
       <c r="AI29" t="n">
         <v>1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AK29" t="n">
-        <v>-5.014160621938001</v>
+        <v>-2.39864696123411</v>
       </c>
       <c r="AL29" t="n">
-        <v>-3.953715809670997</v>
+        <v>-0.2496601560008559</v>
       </c>
       <c r="AM29" t="n">
-        <v>-3.432089312127443</v>
+        <v>-3.314594947542999</v>
       </c>
       <c r="AN29" t="n">
-        <v>-3.939052411763074</v>
+        <v>-0.7181060714421933</v>
       </c>
       <c r="AO29" t="n">
-        <v>-3.523507998215144</v>
+        <v>-0.3709059846462048</v>
       </c>
       <c r="AP29" t="n">
-        <v>-2.377549723926314</v>
+        <v>-0.6914061039215165</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ZABALA GERARDO</t>
+          <t xml:space="preserve">FRIAS PATRICIA </t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>DNT RONICA REAG</t>
+          <t>DNT CRONCA REAG</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5304,38 +5317,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>70227354</t>
+          <t>70164487</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>KM 6</t>
+          <t>PACARA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>DERIVACION APS</t>
+          <t>PASE DE SALA DE PDIATRIA</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2024-02-19 00:00:00</t>
+          <t>2023-12-19 00:00:00</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>45</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -5344,11 +5357,11 @@
         </is>
       </c>
       <c r="N30" s="2" t="n">
-        <v>45670</v>
+        <v>45674</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>6.65</t>
+          <t>7 ( PESO SECO)</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -5358,22 +5371,22 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>81</t>
         </is>
       </c>
       <c r="U30" t="inlineStr"/>
@@ -5387,22 +5400,22 @@
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERRERA SANDRA </t>
+          <t>TORRES SILVIA</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>DESNUTRICIÓN CRÓNICA MODERADA REAGUDIZADA, DIARREAS INTERMITENTES</t>
+          <t>DESNUTRICIÓN MARASMO KWASHIORKOR, ANEMIA CRÓNICA, GEA Y TRASTORNOS DEL MEDIO INTERNO EN RESOLUCIÓN</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t xml:space="preserve">INTERNADO </t>
+          <t>INTERNADA</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>FORMULA INDICADA EN INTRNACION F100</t>
+          <t>FORMULA INDICCADA EN INTERNACION F100</t>
         </is>
       </c>
       <c r="AH30" t="inlineStr">
@@ -5414,14 +5427,18 @@
         <v>1</v>
       </c>
       <c r="AJ30" t="inlineStr"/>
-      <c r="AK30" t="n">
-        <v>-3.10117517770075</v>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
       </c>
       <c r="AL30" t="n">
-        <v>-2.284408836368064</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>-2.494402469078453</v>
+        <v>-2.355780856305562</v>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
@@ -5443,12 +5460,12 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUELLAR RICARDO ROMERO JUNIOR </t>
+          <t xml:space="preserve">Isquica Martina </t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DNT CRONICA REAG</t>
+          <t xml:space="preserve">Dnt cronica </t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5458,33 +5475,33 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>70227496</t>
+          <t>70197551</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SALVADOR MAZZA</t>
+          <t>B LA MERCED MOSCONI</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>PASE DE SALA DE PEDIATRIA</t>
+          <t>Consultorios Externos</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2024-03-17 00:00:00</t>
+          <t>2024-01-19 00:00:00</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3,100</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -5494,40 +5511,40 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="N31" s="2" t="n">
-        <v>45709</v>
+        <v>45468</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>5.85</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>61</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="U31" t="inlineStr"/>
@@ -5541,41 +5558,37 @@
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>ROMERO ELENA</t>
+          <t xml:space="preserve">Villareal Silvia </t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>DESNTRICION CRONICA REAGUDIZADA  SOSPECHA DE ABANDONO (MALTRATO INFANITIL) IRAB ARS</t>
+          <t xml:space="preserve">DNT Aguda Calorica Moderada - Retraso del Neurodesarrollo -Microcefalia-Quiste simple Hepatico- Trastorno Deglutorio en estudio </t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>INTERNADA</t>
+          <t>Continua Internada</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>FORMUAL INDICADA EN INTERNACION F100</t>
-        </is>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>WHICHI</t>
-        </is>
-      </c>
+          <t xml:space="preserve">formula de inicio </t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr"/>
       <c r="AI31" t="n">
         <v>1</v>
       </c>
       <c r="AJ31" t="inlineStr"/>
       <c r="AK31" t="n">
-        <v>-4.33173103467363</v>
+        <v>-3.455554733310162</v>
       </c>
       <c r="AL31" t="n">
-        <v>-2.902682164652734</v>
+        <v>-1.513504153567803</v>
       </c>
       <c r="AM31" t="n">
-        <v>-3.814738084036819</v>
+        <v>-3.492394262259693</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
@@ -5597,352 +5610,338 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Arias Mia Rocio</t>
+          <t xml:space="preserve">Gonzalez Luis Antonio </t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">DNT aguda calorica </t>
+          <t>DNT cronica</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>V.O</t>
+          <t>SNG</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>70298049</t>
+          <t>70198574</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SAN SILVESTRE TARTAGAL</t>
+          <t>MISION LA PAZ SVE</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Consultorios Externos</t>
+          <t xml:space="preserve">UTI PEDIATRIA </t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2024-04-16 00:00:00</t>
+          <t>2024-04-27 00:00:00</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2,780</t>
+          <t>2,85</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>48</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>37</t>
         </is>
       </c>
       <c r="N32" s="2" t="n">
-        <v>45468</v>
+        <v>45462</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>49</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-4.2</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.78</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="n">
-        <v>45481</v>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>4.78</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>56.5</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>-0.84</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>-1.31</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>-1.23</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
-      </c>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moreno Angela </t>
+          <t xml:space="preserve">Gonzalez Nilda </t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>DNT Aguda Calorica primaria- Impetigo- ARS</t>
+          <t xml:space="preserve">DNT cronica calorica proteica severasecundaria- Cardiopatia congenita- sindrome genetico e/e </t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t xml:space="preserve">RECUPERADA NUTRICIONALMENTE </t>
+          <t>Continua Internado</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t xml:space="preserve">formula de inicio 90 CC /TOMA AL 18% POR SUCCION </t>
+          <t xml:space="preserve">formula de inicio 60cc/toma al 18% cada 3hs </t>
         </is>
       </c>
       <c r="AH32" t="inlineStr"/>
       <c r="AI32" t="n">
         <v>1</v>
       </c>
-      <c r="AJ32" t="n">
-        <v>13</v>
-      </c>
+      <c r="AJ32" t="inlineStr"/>
       <c r="AK32" t="n">
-        <v>-2.503222670871613</v>
+        <v>-5.279718403685267</v>
       </c>
       <c r="AL32" t="n">
-        <v>-1.430211820142719</v>
+        <v>-4.301158816410321</v>
       </c>
       <c r="AM32" t="n">
-        <v>-2.351984540366294</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>-1.332834557588582</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>-1.248937470017007</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>-0.8662734181628515</v>
+        <v>-4.385695332172435</v>
+      </c>
+      <c r="AN32" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>JUSTINIANO CELESTE  ABIGAIL</t>
+          <t>GONZALEZ  Luis Antonio</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>DNT CRONICA</t>
+          <t>DNT cronica</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>V.O</t>
+          <t>SGN</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>70298051</t>
+          <t>70198574</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">VILLA SAVEDRA </t>
+          <t>Mision La Paz Santa Victoria Este</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>DERIVACION APS</t>
+          <t>HPMI Salta</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2024-04-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
+          <t>2024-04-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>0 A 3 M 27 D</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2.42</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
+          <t>2.285</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="n">
-        <v>45636</v>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>4.88</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>-2.6</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>-3.79</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>-2.91</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="U33" s="2" t="n">
-        <v>45670</v>
-      </c>
+        <v>45526</v>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>Formula de inicioal 18% 70cc cada 3 hs x 8 tomas mas lactancia materna</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>Formula de inicioal 18% 70cc cada 3 hs x 8 tomas mas lactancia materna</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>Formula de inicioal 18% 70cc cada 3 hs x 8 tomas mas lactancia materna</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>Formula de inicioal 18% 70cc cada 3 hs x 8 tomas mas lactancia materna</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>Formula de inicioal 18% 70cc cada 3 hs x 8 tomas mas lactancia materna</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr"/>
-      <c r="AC33" t="inlineStr"/>
+          <t>Formula de inicioal 18% 70cc cada 3 hs x 8 tomas mas lactancia materna</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>Formula de inicioal 18% 70cc cada 3 hs x 8 tomas mas lactancia materna</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Formula de inicioal 18% 70cc cada 3 hs x 8 tomas mas lactancia materna</t>
+        </is>
+      </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>HOGAR DE NIÑOS JUDICIALIZADA</t>
+          <t>Formula de inicioal 18% 70cc cada 3 hs x 8 tomas mas lactancia materna</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>DNT CRONICA SECUNDARIA, DIARREA INTERMITENTE, JUDICIALIZADA, RETRASO DE PAUTAS MADURATIVAS,ARS</t>
+          <t>Formula de inicioal 18% 70cc cada 3 hs x 8 tomas mas lactancia materna</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t xml:space="preserve">RECUPERADA NUTRICIONALMENTE </t>
+          <t>Formula de inicioal 18% 70cc cada 3 hs x 8 tomas mas lactancia materna</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t xml:space="preserve">FORMULA 0% LACTOSA 150CC/TOMA V.O </t>
+          <t>Formula de inicioal 18% 70cc cada 3 hs x 8 tomas mas lactancia materna</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>CRIOLLO</t>
+          <t>wichi</t>
         </is>
       </c>
       <c r="AI33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>-3.906981490575141</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>-2.923997211986509</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>-2.893336098478309</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>-2.14919494620852</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>-2.269516847944234</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>-1.089844337541254</v>
+        <v>2</v>
+      </c>
+      <c r="AJ33" t="inlineStr"/>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="AN33" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torres Licet Maria Cristina </t>
+          <t>ORQUIZO NICOLE</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>DNT cronica</t>
+          <t>DNT CRONICA</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5952,169 +5951,174 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>70298124</t>
+          <t>70198781</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">F </t>
+          <t>F</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">M LA MORA TARTAGAL </t>
+          <t>S.V.E</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Consultorios Externos</t>
+          <t>PASE DE SALA PEDIATRIA</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2024-05-16 00:00:00</t>
+          <t>2024-02-10 00:00:00</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2,32</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
       <c r="N34" s="2" t="n">
-        <v>45468</v>
+        <v>45644</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>62</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>P 10</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>73</t>
         </is>
       </c>
       <c r="U34" s="2" t="n">
-        <v>45477</v>
+        <v>45670</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>5.51</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>64</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>P 25  50</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>P 10   25</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>P25</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>Torres Florencia</t>
+          <t xml:space="preserve">ORQUIZO MARCELA </t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t xml:space="preserve">DNT Proteico Calorica </t>
+          <t>ECNE, DISPLASIA BRONCOPULMONAR, GASTROTOMIA, RGE SEVERO, DESNUTRICIÓN CRÓNICA MODERADA
+2RIA,TRASTORNOS DEGLUTORIOS, ARS</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t xml:space="preserve">RECUPERADA NUTRICIONALMENTE </t>
+          <t xml:space="preserve">DESNUTRICION CRONICA EN RECUPERACION </t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t xml:space="preserve">formula de inicio 65CC 7TOMA AL 18% CADA 3HS </t>
-        </is>
-      </c>
-      <c r="AH34" t="inlineStr"/>
+          <t xml:space="preserve">FORMULA DE INICIO 140CC/TOMA AL 22% 6 TOMAS /D SNG </t>
+        </is>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>CHOROTE</t>
+        </is>
+      </c>
       <c r="AI34" t="n">
         <v>1</v>
       </c>
       <c r="AJ34" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="AK34" t="n">
-        <v>-2.767401071829285</v>
+        <v>-5.014160621938001</v>
       </c>
       <c r="AL34" t="n">
-        <v>-3.196601478751034</v>
+        <v>-3.953715809670997</v>
       </c>
       <c r="AM34" t="n">
-        <v>-1.440996843862405</v>
+        <v>-3.432089312127443</v>
       </c>
       <c r="AN34" t="n">
-        <v>-2.893443790488147</v>
+        <v>-3.939052411763074</v>
       </c>
       <c r="AO34" t="n">
-        <v>-2.911053391140504</v>
+        <v>-3.523507998215144</v>
       </c>
       <c r="AP34" t="n">
-        <v>-1.797338685909245</v>
+        <v>-2.377549723926314</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRIAS IRIS </t>
+          <t>ZABALA GERARDO</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>DNT CRONICA REAG</t>
+          <t>DNT RONICA REAG</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -6124,127 +6128,105 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>SIN DNI</t>
+          <t>70227354</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>S.V.E</t>
+          <t>KM 6</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>PASE DE SALA DE PEDIATRIA</t>
+          <t>DERIVACION APS</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2022-07-14 00:00:00</t>
+          <t>2024-02-19 00:00:00</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr"/>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="n">
-        <v>45665</v>
+        <v>45670</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>8.61</t>
+          <t>6.65</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>-2.49</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>-3.09</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>-2.28</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>-1.13</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>-3.24</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>-3.57</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="n">
-        <v>45313</v>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>10.29</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>0.24</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>-2.4</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>-3.3</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr"/>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>CEBALLOS MARILINA</t>
+          <t xml:space="preserve">HERRERA SANDRA </t>
         </is>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>DESNUTRICIÓN CRÓNICA REAGUDIZADA MODERADA, TRASTORNOS METABOLICOS EN RESOLUCIÓN, GEA EN RESOLUCIÓN,</t>
+          <t>DESNUTRICIÓN CRÓNICA MODERADA REAGUDIZADA, DIARREAS INTERMITENTES</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>RECUPERADA NURICIONALMENTE</t>
+          <t xml:space="preserve">INTERNADO </t>
         </is>
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t xml:space="preserve">FORMULA INDICADA EN INTERNACION F100 </t>
+          <t>FORMULA INDICADA EN INTRNACION F100</t>
         </is>
       </c>
       <c r="AH35" t="inlineStr">
@@ -6255,38 +6237,42 @@
       <c r="AI35" t="n">
         <v>1</v>
       </c>
-      <c r="AJ35" t="n">
-        <v>-352</v>
-      </c>
+      <c r="AJ35" t="inlineStr"/>
       <c r="AK35" t="n">
-        <v>-3.268124191428514</v>
+        <v>-3.10117517770075</v>
       </c>
       <c r="AL35" t="n">
-        <v>-3.56902877715708</v>
+        <v>-2.284408836368064</v>
       </c>
       <c r="AM35" t="n">
-        <v>-1.130810614232318</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>-0.003078190438317763</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>-0.6894280825971792</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>0.5572326063779626</v>
+        <v>-2.494402469078453</v>
+      </c>
+      <c r="AN35" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="AP35" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Suarez josefina Isabella</t>
+          <t xml:space="preserve">CUELLAR RICARDO ROMERO JUNIOR </t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">DNT cronica </t>
+          <t>DNT CRONICA REAG</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6294,222 +6280,1236 @@
           <t>SNG</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>70227496</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>cornejo</t>
+          <t>SALVADOR MAZZA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Consultorios Externos</t>
+          <t>PASE DE SALA DE PEDIATRIA</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2024-01-04 00:00:00</t>
+          <t>2024-03-17 00:00:00</t>
         </is>
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>3,14</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>49</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
       <c r="N36" s="2" t="n">
-        <v>45450</v>
+        <v>45709</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>5.85</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>68</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-2.8</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>0.77</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="n">
-        <v>45469</v>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>5.18</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>-1.03</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>-2.71</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>-3.2</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>0.94</t>
-        </is>
-      </c>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr"/>
       <c r="AD36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Milagros Isabelina </t>
+          <t>ROMERO ELENA</t>
         </is>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>DNTcronica calorica moderada- scabiosis- anemia cronica-ARS</t>
+          <t>DESNTRICION CRONICA REAGUDIZADA  SOSPECHA DE ABANDONO (MALTRATO INFANITIL) IRAB ARS</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t xml:space="preserve">RECUPERADA NUTRICIONALMENTE </t>
+          <t>INTERNADA</t>
         </is>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>FORMULA DE INICIO 690CC AL 18% CADA 3HS V.O</t>
-        </is>
-      </c>
-      <c r="AH36" t="inlineStr"/>
-      <c r="AI36" t="inlineStr"/>
-      <c r="AJ36" t="n">
-        <v>19</v>
-      </c>
+          <t>FORMUAL INDICADA EN INTERNACION F100</t>
+        </is>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>WHICHI</t>
+        </is>
+      </c>
+      <c r="AI36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ36" t="inlineStr"/>
       <c r="AK36" t="n">
-        <v>-4.140307111520233</v>
+        <v>-4.33173103467363</v>
       </c>
       <c r="AL36" t="n">
-        <v>-3.103596113718679</v>
+        <v>-2.902682164652734</v>
       </c>
       <c r="AM36" t="n">
-        <v>-3.068973186338715</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>-2.713363895885424</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>-3.226387676021324</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>-1.032214614002564</v>
+        <v>-3.814738084036819</v>
+      </c>
+      <c r="AN36" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="AP36" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>125 A 0 M 22 D</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr"/>
-      <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr"/>
-      <c r="AA37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Arias Mia Rocio</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DNT aguda calorica </t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>V.O</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>70298049</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>SAN SILVESTRE TARTAGAL</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Consultorios Externos</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2024-04-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2,780</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="n">
+        <v>45468</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>3.87</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>-2.32</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>-2.47</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>-1.4</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="n">
+        <v>45481</v>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>4.78</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>-0.84</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>-1.31</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>-1.23</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="inlineStr"/>
-      <c r="AD37" t="inlineStr"/>
-      <c r="AE37" t="inlineStr"/>
-      <c r="AF37" t="inlineStr"/>
-      <c r="AG37" t="inlineStr"/>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moreno Angela </t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>DNT Aguda Calorica primaria- Impetigo- ARS</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RECUPERADA NUTRICIONALMENTE </t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">formula de inicio 90 CC /TOMA AL 18% POR SUCCION </t>
+        </is>
+      </c>
       <c r="AH37" t="inlineStr"/>
-      <c r="AI37" t="inlineStr"/>
-      <c r="AJ37" t="inlineStr"/>
-      <c r="AK37" t="inlineStr">
+      <c r="AI37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>-2.503222670871613</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>-1.430211820142719</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>-2.351984540366294</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>-1.332834557588582</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>-1.248937470017007</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>-0.8662734181628515</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>JUSTINIANO CELESTE  ABIGAIL</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>DNT CRONICA</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>V.O</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>70298051</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VILLA SAVEDRA </t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>DERIVACION APS</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2024-04-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2.42</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" s="2" t="n">
+        <v>45636</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>-2.6</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>-3.79</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>-2.91</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="n">
+        <v>45670</v>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>-1.02</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>-2.15</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>-2.27</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="inlineStr"/>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>HOGAR DE NIÑOS JUDICIALIZADA</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>DNT CRONICA SECUNDARIA, DIARREA INTERMITENTE, JUDICIALIZADA, RETRASO DE PAUTAS MADURATIVAS,ARS</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RECUPERADA NUTRICIONALMENTE </t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FORMULA 0% LACTOSA 150CC/TOMA V.O </t>
+        </is>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>CRIOLLO</t>
+        </is>
+      </c>
+      <c r="AI38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>-3.906981490575141</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>-2.923997211986509</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>-2.893336098478309</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>-2.14919494620852</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>-2.269516847944234</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>-1.089844337541254</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Torres Licet Maria Cristina </t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>DNT cronica</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>70298124</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F </t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M LA MORA TARTAGAL </t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Consultorios Externos</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2024-05-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>2,32</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="n">
+        <v>45468</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>3.08</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>48.5</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>-0.42</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>-0.8</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>-0.9</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="n">
+        <v>45477</v>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>3.24</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>-0.8</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>-0.7</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>0.94</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr"/>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>Torres Florencia</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DNT Proteico Calorica </t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RECUPERADA NUTRICIONALMENTE </t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">formula de inicio 65CC 7TOMA AL 18% CADA 3HS </t>
+        </is>
+      </c>
+      <c r="AH39" t="inlineStr"/>
+      <c r="AI39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>-2.767401071829285</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>-3.196601478751034</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>-1.440996843862405</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>-2.893443790488147</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>-2.911053391140504</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>-1.797338685909245</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FRIAS RITA MARCELA </t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DNT CRONICA </t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>97251739</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>S.V.E</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>PASE DE SALA DE PEDIATRIA</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2023-08-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2.91</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>9.37</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>74.5</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>0.38</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>-0.82</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>-2.31</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="n">
+        <v>45727</v>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>9.45</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>75.5</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>-0.81</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>-2.08</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="inlineStr"/>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASTOR IRENE </t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>DESNUTRICION CRONICA , ANEMIA CRONIC. DISPLASIA BRONCOPULMMONAR E/E. DEFICIENCIA INMUNITARIA PRIMARIA E/E, CARDIOPATIA OCULTA E/E. LACTANTE SIBILANTE, ENFERMEDAD RENAL E/E , DEFICIT DE MICRONUTRIENTES, ARS</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DERIVADA A HPMI </t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>F75 -F100</t>
+        </is>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>WHICHI</t>
+        </is>
+      </c>
+      <c r="AI40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>-0.8176557144441774</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>-2.309878589227692</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>0.8367501000587568</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>-0.8014890811463311</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>-2.069171031154439</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>0.6508876198044315</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FRIAS IRIS </t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>DNT CRONICA REAG</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>SIN DNI</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>S.V.E</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>PASE DE SALA DE PEDIATRIA</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2022-07-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" s="2" t="n">
+        <v>45665</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>8.61</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>-1.13</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>-3.24</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>-3.57</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="n">
+        <v>45313</v>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>10.29</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>0.24</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>-2.4</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>-3.3</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="inlineStr"/>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>CEBALLOS MARILINA</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>DESNUTRICIÓN CRÓNICA REAGUDIZADA MODERADA, TRASTORNOS METABOLICOS EN RESOLUCIÓN, GEA EN RESOLUCIÓN,</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>RECUPERADA NURICIONALMENTE</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FORMULA INDICADA EN INTERNACION F100 </t>
+        </is>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>WHICHI</t>
+        </is>
+      </c>
+      <c r="AI41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>-352</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>-3.268124191428514</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>-3.56902877715708</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>-1.130810614232318</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>-0.003078190438317763</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>-0.6894280825971792</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>0.5572326063779626</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Suarez josefina Isabella</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DNT cronica </t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>cornejo</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Consultorios Externos</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2024-01-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>3,14</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="n">
+        <v>45450</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>57.3</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>-2.8</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>-3.78</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="n">
+        <v>45469</v>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>5.18</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>-1.03</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>-2.71</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>-3.2</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>0.94</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="inlineStr"/>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Milagros Isabelina </t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>DNTcronica calorica moderada- scabiosis- anemia cronica-ARS</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RECUPERADA NUTRICIONALMENTE </t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>FORMULA DE INICIO 690CC AL 18% CADA 3HS V.O</t>
+        </is>
+      </c>
+      <c r="AH42" t="inlineStr"/>
+      <c r="AI42" t="inlineStr"/>
+      <c r="AJ42" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>-4.140307111520233</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>-3.103596113718679</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>-3.068973186338715</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>-2.713363895885424</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>-3.226387676021324</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>-1.032214614002564</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>125 A 2 M 18 D</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="inlineStr"/>
+      <c r="AD43" t="inlineStr"/>
+      <c r="AE43" t="inlineStr"/>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="inlineStr"/>
+      <c r="AH43" t="inlineStr"/>
+      <c r="AI43" t="inlineStr"/>
+      <c r="AJ43" t="inlineStr"/>
+      <c r="AK43" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="AL37" t="inlineStr">
+      <c r="AL43" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
+      <c r="AM43" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="AN37" t="inlineStr">
+      <c r="AN43" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="AO37" t="inlineStr">
+      <c r="AO43" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="AP37" t="inlineStr">
+      <c r="AP43" t="inlineStr">
         <is>
           <t>error</t>
         </is>
